--- a/diss/prrzlm.xlsx
+++ b/diss/prrzlm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\PVT_TSU\diss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49D19904-0B02-4CD3-87C5-AE10DA815B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D11626B-4133-4E40-BDF8-54C343E99456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="49">
   <si>
     <t>C6</t>
   </si>
@@ -184,9 +184,6 @@
   <si>
     <t>t sat</t>
   </si>
-  <si>
-    <t>40 rows × 40 columns</t>
-  </si>
 </sst>
 </file>
 
@@ -501,152 +498,161 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>phase_env!$E$2:$AZ$2</c:f>
+              <c:f>phase_env!$B$2:$AZ$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="48"/>
+                <c:ptCount val="51"/>
                 <c:pt idx="0">
+                  <c:v>6.8434570299999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.4556152300000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.03862305</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>8.6021972699999996</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="4">
                   <c:v>9.1366210900000002</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
                   <c:v>9.6321777300000004</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="6">
                   <c:v>10.10830078</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="7">
                   <c:v>10.53583984</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
                   <c:v>10.94394531</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="9">
                   <c:v>11.31318359</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="10">
                   <c:v>11.66298828</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="11">
                   <c:v>11.97392578</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="12">
                   <c:v>12.25571289</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="13">
                   <c:v>12.49863281</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="14">
                   <c:v>12.73183594</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="15">
                   <c:v>12.92617188</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="16">
                   <c:v>13.101074219999999</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="17">
                   <c:v>13.23710938</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="18">
                   <c:v>13.353710939999999</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="19">
                   <c:v>13.4703125</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="20">
                   <c:v>13.52861328</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="21">
                   <c:v>13.58691406</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="22">
                   <c:v>13.625781249999999</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="23">
                   <c:v>13.625781249999999</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="24">
                   <c:v>13.625781249999999</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="25">
                   <c:v>13.58691406</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="26">
                   <c:v>13.548046879999999</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="27">
                   <c:v>13.489746090000001</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="28">
                   <c:v>13.412011720000001</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="29">
                   <c:v>13.31484375</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="30">
                   <c:v>13.19824219</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="31">
                   <c:v>13.081640630000001</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="32">
                   <c:v>12.92617188</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="33">
                   <c:v>12.770703129999999</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="34">
                   <c:v>12.576367189999999</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="35">
                   <c:v>12.382031250000001</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="36">
                   <c:v>12.187695310000001</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="37">
                   <c:v>11.95449219</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="38">
                   <c:v>11.68242188</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="39">
                   <c:v>11.410351560000001</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="40">
                   <c:v>11.13828125</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="41">
                   <c:v>10.827343750000001</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="42">
                   <c:v>10.438671879999999</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="43">
                   <c:v>10.050000000000001</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="44">
                   <c:v>9.6613281299999993</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="45">
                   <c:v>9.1171875</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="46">
                   <c:v>8.4953125000000007</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="47">
                   <c:v>7.5625</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="48">
                   <c:v>7.2515625000000004</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="49">
                   <c:v>6.6296875000000002</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="50">
                   <c:v>5.6968750000000004</c:v>
                 </c:pt>
               </c:numCache>
@@ -1065,7 +1071,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>58.4</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1077,7 +1083,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>12.047000000000001</c:v>
+                  <c:v>13.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1276,7 +1282,1056 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>phase_env!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>kesler</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>phase_env!$B$1:$AZ$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>410</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>430</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>440</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>460</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>470</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>510</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>phase_env!$B$2:$AZ$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>6.8434570299999997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.4556152300000003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.03862305</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.6021972699999996</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.1366210900000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.6321777300000004</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>10.10830078</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10.53583984</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>10.94394531</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11.31318359</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11.66298828</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>11.97392578</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12.25571289</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12.49863281</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.73183594</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>12.92617188</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>13.101074219999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>13.23710938</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>13.353710939999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>13.4703125</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>13.52861328</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>13.58691406</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>13.625781249999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>13.625781249999999</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>13.625781249999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>13.58691406</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>13.548046879999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>13.489746090000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>13.412011720000001</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>13.31484375</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>13.19824219</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>13.081640630000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.92617188</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>12.770703129999999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>12.576367189999999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>12.382031250000001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>12.187695310000001</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>11.95449219</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>11.68242188</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>11.410351560000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>11.13828125</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>10.827343750000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>10.438671879999999</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>10.050000000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>9.6613281299999993</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>9.1171875</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8.4953125000000007</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>7.5625</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>7.2515625000000004</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>6.6296875000000002</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5.6968750000000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0ABD-414A-9D37-BD563B238938}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>phase_env!$A$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>base</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>phase_env!$B$1:$AZ$1</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>410</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>430</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>440</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>460</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>470</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>510</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>phase_env!$B$3:$AZ$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="51"/>
+                <c:pt idx="0">
+                  <c:v>5.8717773400000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.4110595699999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.9309082000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.4264648400000004</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.9025878900000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8.3592773400000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.7868164100000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.1754882799999997</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.5447265600000009</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.89453125</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10.20546875</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10.496972660000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10.75932617</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>11.00224609</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>11.216015629999999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>11.39091797</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>11.565820309999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>11.70185547</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>11.818457029999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>11.915625</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>11.993359379999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>12.051660160000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>12.09052734</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>12.109960940000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>12.129394530000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12.109960940000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>12.071093749999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>12.03222656</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>11.97392578</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>11.89619141</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>11.818457029999999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>11.70185547</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>11.58525391</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>11.44921875</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>11.293749999999999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>11.13828125</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>10.963378909999999</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>10.769042969999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>10.555273440000001</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>10.322070310000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>10.08886719</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>9.8167968800000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>9.5058593800000004</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>9.1949218800000008</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8.8062500000000004</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8.4953125000000007</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8.0289062500000004</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>7.5625</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>6.9406249999999998</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>6.3187499999999996</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5.6968750000000004</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0ABD-414A-9D37-BD563B238938}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>P sat fact</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>phase_env!$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>phase_env!$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>13.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0ABD-414A-9D37-BD563B238938}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2032487008"/>
+        <c:axId val="2032492000"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2032487008"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="70"/>
+          <c:min val="50"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2032492000"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="2"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2032492000"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2032487008"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1832,6 +2887,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1865,6 +3436,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44CC1AF3-9D14-4916-B07E-C134BC07B577}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3737,9 +5346,7 @@
       <c r="AH46" s="2"/>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="M48" s="3" t="s">
-        <v>49</v>
-      </c>
+      <c r="M48" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4230,7 +5837,7 @@
         <v>47</v>
       </c>
       <c r="B7">
-        <v>12.047000000000001</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="8" spans="1:52" x14ac:dyDescent="0.25">
@@ -4238,7 +5845,7 @@
         <v>48</v>
       </c>
       <c r="B8">
-        <v>58.4</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
